--- a/data-source/食物_药数据.xlsx
+++ b/data-source/食物_药数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88BC13AB-0678-43BA-AC01-AF308A22F423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA88CC7-6415-4DA5-9595-B5F83E2773B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -273,9 +273,6 @@
     <t>胡萝卜</t>
   </si>
   <si>
-    <t>给马匹恢复10点饱食度100经验值。玩家可以直接吃</t>
-  </si>
-  <si>
     <t>配方</t>
   </si>
   <si>
@@ -463,6 +460,9 @@
   </si>
   <si>
     <t>瞬间120，持续240</t>
+  </si>
+  <si>
+    <t>给马匹恢复10点饱食度100经验值。玩家可以直接吃；大车炮台掉落</t>
   </si>
 </sst>
 </file>
@@ -1029,7 +1029,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -1040,7 +1040,7 @@
     </row>
     <row r="2" spans="1:7" ht="15" thickTop="1" thickBot="1">
       <c r="A2" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -1049,16 +1049,16 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="F2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="25.9" thickTop="1">
@@ -1069,15 +1069,15 @@
         <v>3</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="38.25">
@@ -1091,10 +1091,10 @@
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1108,10 +1108,10 @@
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="51">
@@ -1127,10 +1127,10 @@
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1148,10 +1148,10 @@
         <v>40</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="25.5">
@@ -1169,10 +1169,10 @@
         <v>10</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1188,10 +1188,10 @@
         <v>40</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="25.5">
@@ -1207,10 +1207,10 @@
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1228,10 +1228,10 @@
         <v>25</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1249,10 +1249,10 @@
         <v>5</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="25.5">
@@ -1268,10 +1268,10 @@
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="25.5">
@@ -1289,10 +1289,10 @@
         <v>20</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1310,10 +1310,10 @@
         <v>20</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1329,10 +1329,10 @@
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1348,10 +1348,10 @@
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1369,10 +1369,10 @@
         <v>80</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="51">
@@ -1390,10 +1390,10 @@
         <v>-3</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1411,10 +1411,10 @@
         <v>-5</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1430,10 +1430,10 @@
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1449,10 +1449,10 @@
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="25.5">
@@ -1470,10 +1470,10 @@
         <v>25</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1491,15 +1491,15 @@
         <v>10</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>29</v>
@@ -1512,10 +1512,10 @@
         <v>30</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1535,10 +1535,10 @@
         <v>-3</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="25.5">
@@ -1558,10 +1558,10 @@
         <v>-5</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1575,10 +1575,10 @@
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1596,10 +1596,10 @@
         <v>23</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="25.5">
@@ -1607,7 +1607,7 @@
         <v>81</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="C30" s="5">
         <v>40</v>
@@ -1619,10 +1619,10 @@
         <v>10</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1638,10 +1638,10 @@
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1659,15 +1659,15 @@
         <v>-3</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="25.5">
       <c r="A33" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
@@ -1680,15 +1680,15 @@
         <v>20</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
@@ -1701,10 +1701,10 @@
         <v>3</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1722,10 +1722,10 @@
         <v>2</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="63.75">
@@ -1743,10 +1743,10 @@
         <v>30</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1764,10 +1764,10 @@
         <v>-5</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1785,10 +1785,10 @@
         <v>20</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1806,15 +1806,15 @@
         <v>5</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
@@ -1825,10 +1825,10 @@
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1846,10 +1846,10 @@
         <v>45</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1867,10 +1867,10 @@
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1886,10 +1886,10 @@
         <v>30</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1907,10 +1907,10 @@
         <v>-10</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1928,10 +1928,10 @@
         <v>2</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1951,10 +1951,10 @@
         <v>2</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1974,10 +1974,10 @@
         <v>2</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1995,15 +1995,15 @@
         <v>3</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>29</v>
@@ -2018,15 +2018,15 @@
         <v>3</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
@@ -2037,10 +2037,10 @@
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2060,15 +2060,15 @@
         <v>3</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
@@ -2081,10 +2081,10 @@
         <v>3</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="28.15" customHeight="1">
@@ -2104,15 +2104,15 @@
         <v>3</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>53</v>
@@ -2127,15 +2127,15 @@
         <v>-10</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -2144,10 +2144,10 @@
         <v>40</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2161,10 +2161,10 @@
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
       <c r="F56" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -2178,10 +2178,10 @@
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
       <c r="F57" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="25.5">
@@ -2195,10 +2195,10 @@
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
       <c r="F58" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2212,10 +2212,10 @@
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
       <c r="F59" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -2229,10 +2229,10 @@
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
       <c r="F60" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="38.25">
@@ -2246,10 +2246,10 @@
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
       <c r="F61" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="25.5">
@@ -2263,10 +2263,10 @@
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
       <c r="F62" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2280,10 +2280,10 @@
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
       <c r="F63" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="25.5">
@@ -2297,10 +2297,10 @@
       <c r="D64" s="5"/>
       <c r="E64" s="5"/>
       <c r="F64" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="25.5">
@@ -2314,10 +2314,10 @@
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
       <c r="F65" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -2331,10 +2331,10 @@
       <c r="D66" s="5"/>
       <c r="E66" s="5"/>
       <c r="F66" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="G66" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="G66" s="6" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="14.65" thickBot="1">
@@ -2348,10 +2348,10 @@
       <c r="D67" s="10"/>
       <c r="E67" s="10"/>
       <c r="F67" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G67" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/食物_药数据.xlsx
+++ b/data-source/食物_药数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA88CC7-6415-4DA5-9595-B5F83E2773B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11505A71-2F9F-4121-855B-888D4D70CDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="144">
   <si>
     <t>特殊效果</t>
   </si>
@@ -463,6 +463,12 @@
   </si>
   <si>
     <t>给马匹恢复10点饱食度100经验值。玩家可以直接吃；大车炮台掉落</t>
+  </si>
+  <si>
+    <t>重型绷带</t>
+  </si>
+  <si>
+    <t>瞬间150</t>
   </si>
 </sst>
 </file>
@@ -1015,7 +1021,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.265625" customWidth="1"/>
@@ -1194,41 +1200,37 @@
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="25.5">
+    <row r="10" spans="1:7">
       <c r="A10" s="12" t="s">
-        <v>13</v>
+        <v>142</v>
       </c>
       <c r="B10" s="5"/>
-      <c r="C10" s="5">
-        <v>130</v>
-      </c>
-      <c r="D10" s="5">
-        <v>100</v>
-      </c>
+      <c r="C10" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="25.5">
       <c r="A11" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
+        <v>130</v>
+      </c>
+      <c r="D11" s="5">
         <v>100</v>
       </c>
-      <c r="D11" s="5">
-        <v>80</v>
-      </c>
-      <c r="E11" s="5">
-        <v>25</v>
-      </c>
+      <c r="E11" s="5"/>
       <c r="F11" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>84</v>
@@ -1236,100 +1238,102 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
         <v>100</v>
       </c>
       <c r="D12" s="5">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E12" s="5">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="25.5">
-      <c r="A13" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>10</v>
-      </c>
+    <row r="13" spans="1:7">
+      <c r="A13" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="5"/>
       <c r="C13" s="5">
         <v>100</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
+      <c r="D13" s="5">
+        <v>75</v>
+      </c>
+      <c r="E13" s="5">
+        <v>5</v>
+      </c>
       <c r="F13" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="25.5">
+      <c r="A14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="5">
+        <v>100</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G14" s="6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="25.5">
-      <c r="A14" s="12" t="s">
+    <row r="15" spans="1:7" ht="25.5">
+      <c r="A15" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B15" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C15" s="5">
         <v>90</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5">
-        <v>20</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5">
-        <v>80</v>
-      </c>
-      <c r="D15" s="5">
-        <v>70</v>
-      </c>
+      <c r="D15" s="5"/>
       <c r="E15" s="5">
         <v>20</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="7" t="s">
-        <v>20</v>
+      <c r="A16" s="12" t="s">
+        <v>19</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
         <v>80</v>
       </c>
       <c r="D16" s="5">
-        <v>40</v>
-      </c>
-      <c r="E16" s="5"/>
+        <v>70</v>
+      </c>
+      <c r="E16" s="5">
+        <v>20</v>
+      </c>
       <c r="F16" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>84</v>
@@ -1337,89 +1341,87 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
         <v>80</v>
       </c>
       <c r="D17" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="12" t="s">
-        <v>22</v>
+      <c r="A18" s="7" t="s">
+        <v>21</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
         <v>80</v>
       </c>
       <c r="D18" s="5">
-        <v>10</v>
-      </c>
-      <c r="E18" s="5">
-        <v>80</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="E18" s="5"/>
       <c r="F18" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="51">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D19" s="5">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E19" s="5">
-        <v>-3</v>
+        <v>80</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="7" t="s">
-        <v>24</v>
+    <row r="20" spans="1:7" ht="51">
+      <c r="A20" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D20" s="5">
         <v>30</v>
       </c>
       <c r="E20" s="5">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
@@ -1428,7 +1430,9 @@
       <c r="D21" s="5">
         <v>30</v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="E21" s="5">
+        <v>-5</v>
+      </c>
       <c r="F21" s="5" t="s">
         <v>103</v>
       </c>
@@ -1438,47 +1442,45 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="D22" s="5">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="25.5">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
         <v>50</v>
       </c>
       <c r="D23" s="5">
-        <v>45</v>
-      </c>
-      <c r="E23" s="5">
-        <v>25</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="E23" s="5"/>
       <c r="F23" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="25.5">
       <c r="A24" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
@@ -1488,92 +1490,96 @@
         <v>45</v>
       </c>
       <c r="E24" s="5">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>29</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="B25" s="5"/>
       <c r="C25" s="5">
         <v>50</v>
       </c>
-      <c r="D25" s="5"/>
+      <c r="D25" s="5">
+        <v>45</v>
+      </c>
       <c r="E25" s="5">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="7" t="s">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C26" s="5">
         <v>50</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="5"/>
+      <c r="E26" s="5">
+        <v>30</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="5">
+        <v>50</v>
+      </c>
+      <c r="D27" s="5">
         <v>40</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E27" s="5">
         <v>-3</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F27" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G27" s="6" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="25.5">
-      <c r="A27" s="7" t="s">
+    <row r="28" spans="1:7" ht="25.5">
+      <c r="A28" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B28" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C28" s="5">
         <v>45</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D28" s="5">
         <v>10</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E28" s="5">
         <v>-5</v>
       </c>
-      <c r="F27" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5">
-        <v>40</v>
-      </c>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
       <c r="F28" s="5" t="s">
         <v>103</v>
       </c>
@@ -1583,230 +1589,226 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
+        <v>40</v>
+      </c>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5">
         <v>50</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D30" s="5">
         <v>37</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E30" s="5">
         <v>23</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F30" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G30" s="6" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="25.5">
-      <c r="A30" s="12" t="s">
+    <row r="31" spans="1:7" ht="25.5">
+      <c r="A31" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B31" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C30" s="5">
-        <v>40</v>
-      </c>
-      <c r="D30" s="5">
-        <v>15</v>
-      </c>
-      <c r="E30" s="5">
-        <v>10</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="5"/>
       <c r="C31" s="5">
         <v>40</v>
       </c>
       <c r="D31" s="5">
-        <v>20</v>
-      </c>
-      <c r="E31" s="5"/>
+        <v>15</v>
+      </c>
+      <c r="E31" s="5">
+        <v>10</v>
+      </c>
       <c r="F31" s="5" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
         <v>40</v>
       </c>
       <c r="D32" s="5">
-        <v>40</v>
-      </c>
-      <c r="E32" s="5">
-        <v>-3</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="E32" s="5"/>
       <c r="F32" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="25.5">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" s="7" t="s">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D33" s="5">
         <v>40</v>
       </c>
       <c r="E33" s="5">
-        <v>20</v>
+        <v>-3</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="25.5">
       <c r="A34" s="7" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D34" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E34" s="5">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="7" t="s">
-        <v>38</v>
+        <v>132</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
         <v>30</v>
       </c>
       <c r="D35" s="5">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E35" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="63.75">
+    <row r="36" spans="1:7">
       <c r="A36" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
         <v>30</v>
       </c>
       <c r="D36" s="5">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E36" s="5">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="63.75">
       <c r="A37" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D37" s="5">
         <v>10</v>
       </c>
       <c r="E37" s="5">
-        <v>-5</v>
+        <v>30</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D38" s="5">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E38" s="5">
-        <v>20</v>
+        <v>-5</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D39" s="5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E39" s="5">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>120</v>
@@ -1814,7 +1816,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="7" t="s">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
@@ -1823,49 +1825,49 @@
       <c r="D40" s="5">
         <v>15</v>
       </c>
-      <c r="E40" s="5"/>
+      <c r="E40" s="5">
+        <v>5</v>
+      </c>
       <c r="F40" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="12" t="s">
-        <v>80</v>
+      <c r="A41" s="7" t="s">
+        <v>124</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D41" s="5">
         <v>15</v>
       </c>
-      <c r="E41" s="5">
-        <v>45</v>
-      </c>
+      <c r="E41" s="5"/>
       <c r="F41" s="5" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>29</v>
-      </c>
+      <c r="A42" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" s="5"/>
       <c r="C42" s="5">
         <v>10</v>
       </c>
       <c r="D42" s="5">
-        <v>10</v>
-      </c>
-      <c r="E42" s="5"/>
+        <v>15</v>
+      </c>
+      <c r="E42" s="5">
+        <v>45</v>
+      </c>
       <c r="F42" s="5" t="s">
         <v>103</v>
       </c>
@@ -1875,16 +1877,18 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B43" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="C43" s="5">
         <v>10</v>
       </c>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5">
-        <v>30</v>
-      </c>
+      <c r="D43" s="5">
+        <v>10</v>
+      </c>
+      <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
         <v>103</v>
       </c>
@@ -1894,17 +1898,15 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
         <v>10</v>
       </c>
-      <c r="D44" s="5">
-        <v>15</v>
-      </c>
+      <c r="D44" s="5"/>
       <c r="E44" s="5">
-        <v>-10</v>
+        <v>30</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>103</v>
@@ -1915,17 +1917,17 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D45" s="5">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E45" s="5">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>103</v>
@@ -1936,11 +1938,9 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>48</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="B46" s="5"/>
       <c r="C46" s="5">
         <v>9</v>
       </c>
@@ -1959,10 +1959,10 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C47" s="5">
         <v>9</v>
@@ -1982,17 +1982,19 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="B48" s="5"/>
+        <v>49</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="C48" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D48" s="5">
+        <v>4</v>
+      </c>
+      <c r="E48" s="5">
         <v>2</v>
-      </c>
-      <c r="E48" s="5">
-        <v>3</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>103</v>
@@ -2003,11 +2005,9 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>29</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B49" s="5"/>
       <c r="C49" s="5">
         <v>7</v>
       </c>
@@ -2025,40 +2025,40 @@
       </c>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="12" t="s">
+      <c r="A50" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C50" s="5">
+        <v>7</v>
+      </c>
+      <c r="D50" s="5">
+        <v>2</v>
+      </c>
+      <c r="E50" s="5">
+        <v>3</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5">
-        <v>5</v>
-      </c>
-      <c r="D50" s="5">
-        <v>7</v>
-      </c>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>53</v>
-      </c>
+      <c r="B51" s="5"/>
       <c r="C51" s="5">
         <v>5</v>
       </c>
       <c r="D51" s="5">
-        <v>2</v>
-      </c>
-      <c r="E51" s="5">
-        <v>3</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E51" s="5"/>
       <c r="F51" s="5" t="s">
         <v>103</v>
       </c>
@@ -2068,14 +2068,16 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B52" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="C52" s="5">
         <v>5</v>
       </c>
       <c r="D52" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E52" s="5">
         <v>3</v>
@@ -2087,18 +2089,16 @@
         <v>103</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="28.15" customHeight="1">
+    <row r="53" spans="1:7">
       <c r="A53" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>55</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D53" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E53" s="5">
         <v>3</v>
@@ -2110,56 +2110,62 @@
         <v>103</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" ht="28.15" customHeight="1">
       <c r="A54" s="7" t="s">
-        <v>126</v>
+        <v>54</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C54" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D54" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E54" s="5">
-        <v>-10</v>
+        <v>3</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B55" s="5"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
+        <v>126</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C55" s="5">
+        <v>1</v>
+      </c>
+      <c r="D55" s="5">
+        <v>5</v>
+      </c>
       <c r="E55" s="5">
-        <v>40</v>
+        <v>-10</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>57</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="B56" s="5"/>
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
+      <c r="E56" s="5">
+        <v>40</v>
+      </c>
       <c r="F56" s="5" t="s">
         <v>103</v>
       </c>
@@ -2169,10 +2175,10 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
@@ -2184,12 +2190,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="25.5">
-      <c r="A58" s="12" t="s">
-        <v>60</v>
+    <row r="58" spans="1:7">
+      <c r="A58" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
@@ -2201,12 +2207,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
-      <c r="A59" s="8" t="s">
-        <v>62</v>
+    <row r="59" spans="1:7" ht="25.5">
+      <c r="A59" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
@@ -2219,11 +2225,11 @@
       </c>
     </row>
     <row r="60" spans="1:7">
-      <c r="A60" s="7" t="s">
-        <v>64</v>
+      <c r="A60" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
@@ -2235,12 +2241,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="38.25">
-      <c r="A61" s="8" t="s">
-        <v>66</v>
+    <row r="61" spans="1:7">
+      <c r="A61" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
@@ -2252,12 +2258,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="25.5">
-      <c r="A62" s="12" t="s">
-        <v>68</v>
+    <row r="62" spans="1:7" ht="38.25">
+      <c r="A62" s="8" t="s">
+        <v>66</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C62" s="5"/>
       <c r="D62" s="5"/>
@@ -2269,12 +2275,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
-      <c r="A63" s="8" t="s">
-        <v>70</v>
+    <row r="63" spans="1:7" ht="25.5">
+      <c r="A63" s="12" t="s">
+        <v>68</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
@@ -2286,12 +2292,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="25.5">
-      <c r="A64" s="12" t="s">
-        <v>72</v>
+    <row r="64" spans="1:7">
+      <c r="A64" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5"/>
@@ -2305,10 +2311,10 @@
     </row>
     <row r="65" spans="1:7" ht="25.5">
       <c r="A65" s="12" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
@@ -2320,37 +2326,54 @@
         <v>103</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
-      <c r="A66" s="8" t="s">
-        <v>76</v>
+    <row r="66" spans="1:7" ht="25.5">
+      <c r="A66" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C66" s="5"/>
       <c r="D66" s="5"/>
       <c r="E66" s="5"/>
       <c r="F66" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G66" s="6" t="s">
+      <c r="G67" s="6" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A67" s="9" t="s">
+    <row r="68" spans="1:7" ht="14.65" thickBot="1">
+      <c r="A68" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B67" s="10" t="s">
+      <c r="B68" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="C67" s="10"/>
-      <c r="D67" s="10"/>
-      <c r="E67" s="10"/>
-      <c r="F67" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="G67" s="11" t="s">
+      <c r="C68" s="10"/>
+      <c r="D68" s="10"/>
+      <c r="E68" s="10"/>
+      <c r="F68" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="G68" s="11" t="s">
         <v>103</v>
       </c>
     </row>

--- a/data-source/食物_药数据.xlsx
+++ b/data-source/食物_药数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11505A71-2F9F-4121-855B-888D4D70CDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B1EF74-5370-4BF0-8948-CA63A2FBC073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,12 +25,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="167">
   <si>
     <t>特殊效果</t>
-  </si>
-  <si>
-    <t>持续治愈</t>
   </si>
   <si>
     <t>僧侣药酒</t>
@@ -469,6 +466,78 @@
   </si>
   <si>
     <t>瞬间150</t>
+  </si>
+  <si>
+    <t>治愈</t>
+  </si>
+  <si>
+    <t>持续200</t>
+  </si>
+  <si>
+    <t>持续160</t>
+  </si>
+  <si>
+    <t>持续150</t>
+  </si>
+  <si>
+    <t>持续130</t>
+  </si>
+  <si>
+    <t>持续100</t>
+  </si>
+  <si>
+    <t>持续90</t>
+  </si>
+  <si>
+    <t>持续80</t>
+  </si>
+  <si>
+    <t>持续75</t>
+  </si>
+  <si>
+    <t>持续70</t>
+  </si>
+  <si>
+    <t>持续50</t>
+  </si>
+  <si>
+    <t>持续45</t>
+  </si>
+  <si>
+    <t>持续40</t>
+  </si>
+  <si>
+    <t>持续35</t>
+  </si>
+  <si>
+    <t>持续30</t>
+  </si>
+  <si>
+    <t>持续25</t>
+  </si>
+  <si>
+    <t>持续20</t>
+  </si>
+  <si>
+    <t>持续15</t>
+  </si>
+  <si>
+    <t>持续10</t>
+  </si>
+  <si>
+    <t>持续9</t>
+  </si>
+  <si>
+    <t>持续7</t>
+  </si>
+  <si>
+    <t>持续5</t>
+  </si>
+  <si>
+    <t>持续4</t>
+  </si>
+  <si>
+    <t>持续1</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +1104,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -1046,127 +1115,127 @@
     </row>
     <row r="2" spans="1:7" ht="15" thickTop="1" thickBot="1">
       <c r="A2" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1</v>
+        <v>143</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="F2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="25.9" thickTop="1">
       <c r="A3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>3</v>
-      </c>
       <c r="C3" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="38.25">
       <c r="A4" s="7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="51">
       <c r="A6" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="5">
-        <v>200</v>
+        <v>2</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="5">
-        <v>160</v>
+      <c r="C7" s="5" t="s">
+        <v>145</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5">
         <v>40</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="25.5">
       <c r="A8" s="12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="5"/>
-      <c r="C8" s="5">
-        <v>150</v>
+      <c r="C8" s="5" t="s">
+        <v>146</v>
       </c>
       <c r="D8" s="5">
         <v>100</v>
@@ -1175,74 +1244,74 @@
         <v>10</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="5"/>
-      <c r="C9" s="5">
-        <v>150</v>
+      <c r="C9" s="5" t="s">
+        <v>146</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5">
         <v>40</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="25.5">
       <c r="A11" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" s="5"/>
-      <c r="C11" s="5">
-        <v>130</v>
+      <c r="C11" s="5" t="s">
+        <v>147</v>
       </c>
       <c r="D11" s="5">
         <v>100</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" s="5"/>
-      <c r="C12" s="5">
-        <v>100</v>
+      <c r="C12" s="5" t="s">
+        <v>148</v>
       </c>
       <c r="D12" s="5">
         <v>80</v>
@@ -1251,19 +1320,19 @@
         <v>25</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" s="5"/>
-      <c r="C13" s="5">
-        <v>100</v>
+      <c r="C13" s="5" t="s">
+        <v>148</v>
       </c>
       <c r="D13" s="5">
         <v>75</v>
@@ -1272,59 +1341,59 @@
         <v>5</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="25.5">
       <c r="A14" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="5">
-        <v>100</v>
+        <v>9</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>148</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="25.5">
       <c r="A15" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="5">
-        <v>90</v>
+      <c r="C15" s="5" t="s">
+        <v>149</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5">
         <v>20</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="5"/>
-      <c r="C16" s="5">
-        <v>80</v>
+      <c r="C16" s="5" t="s">
+        <v>150</v>
       </c>
       <c r="D16" s="5">
         <v>70</v>
@@ -1333,57 +1402,57 @@
         <v>20</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" s="5"/>
-      <c r="C17" s="5">
-        <v>80</v>
+      <c r="C17" s="5" t="s">
+        <v>150</v>
       </c>
       <c r="D17" s="5">
         <v>40</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" s="5"/>
-      <c r="C18" s="5">
-        <v>80</v>
+      <c r="C18" s="5" t="s">
+        <v>150</v>
       </c>
       <c r="D18" s="5">
         <v>30</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" s="5"/>
-      <c r="C19" s="5">
-        <v>80</v>
+      <c r="C19" s="5" t="s">
+        <v>150</v>
       </c>
       <c r="D19" s="5">
         <v>10</v>
@@ -1392,19 +1461,19 @@
         <v>80</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="51">
       <c r="A20" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" s="5"/>
-      <c r="C20" s="5">
-        <v>75</v>
+      <c r="C20" s="5" t="s">
+        <v>151</v>
       </c>
       <c r="D20" s="5">
         <v>30</v>
@@ -1413,19 +1482,19 @@
         <v>-3</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21" s="5"/>
-      <c r="C21" s="5">
-        <v>70</v>
+      <c r="C21" s="5" t="s">
+        <v>152</v>
       </c>
       <c r="D21" s="5">
         <v>30</v>
@@ -1434,57 +1503,57 @@
         <v>-5</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" s="5"/>
-      <c r="C22" s="5">
-        <v>70</v>
+      <c r="C22" s="5" t="s">
+        <v>152</v>
       </c>
       <c r="D22" s="5">
         <v>30</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" s="5"/>
-      <c r="C23" s="5">
-        <v>50</v>
+      <c r="C23" s="5" t="s">
+        <v>153</v>
       </c>
       <c r="D23" s="5">
         <v>60</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="25.5">
       <c r="A24" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24" s="5"/>
-      <c r="C24" s="5">
-        <v>50</v>
+      <c r="C24" s="5" t="s">
+        <v>153</v>
       </c>
       <c r="D24" s="5">
         <v>45</v>
@@ -1493,19 +1562,19 @@
         <v>25</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25" s="5"/>
-      <c r="C25" s="5">
-        <v>50</v>
+      <c r="C25" s="5" t="s">
+        <v>153</v>
       </c>
       <c r="D25" s="5">
         <v>45</v>
@@ -1514,42 +1583,42 @@
         <v>10</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="5">
-        <v>50</v>
+        <v>28</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>153</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5">
         <v>30</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="5">
-        <v>50</v>
+      <c r="C27" s="5" t="s">
+        <v>153</v>
       </c>
       <c r="D27" s="5">
         <v>40</v>
@@ -1558,21 +1627,21 @@
         <v>-3</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="25.5">
       <c r="A28" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" s="5">
-        <v>45</v>
+      <c r="C28" s="5" t="s">
+        <v>154</v>
       </c>
       <c r="D28" s="5">
         <v>10</v>
@@ -1581,36 +1650,36 @@
         <v>-5</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" s="5"/>
-      <c r="C29" s="5">
-        <v>40</v>
+      <c r="C29" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" s="5"/>
-      <c r="C30" s="5">
-        <v>50</v>
+      <c r="C30" s="5" t="s">
+        <v>153</v>
       </c>
       <c r="D30" s="5">
         <v>37</v>
@@ -1619,21 +1688,21 @@
         <v>23</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="25.5">
       <c r="A31" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C31" s="5">
-        <v>40</v>
+        <v>140</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="D31" s="5">
         <v>15</v>
@@ -1642,38 +1711,38 @@
         <v>10</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B32" s="5"/>
-      <c r="C32" s="5">
-        <v>40</v>
+      <c r="C32" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="D32" s="5">
         <v>20</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B33" s="5"/>
-      <c r="C33" s="5">
-        <v>40</v>
+      <c r="C33" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="D33" s="5">
         <v>40</v>
@@ -1682,19 +1751,19 @@
         <v>-3</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="25.5">
       <c r="A34" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B34" s="5"/>
-      <c r="C34" s="5">
-        <v>35</v>
+      <c r="C34" s="5" t="s">
+        <v>156</v>
       </c>
       <c r="D34" s="5">
         <v>40</v>
@@ -1703,19 +1772,19 @@
         <v>20</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B35" s="5"/>
-      <c r="C35" s="5">
-        <v>30</v>
+      <c r="C35" s="5" t="s">
+        <v>157</v>
       </c>
       <c r="D35" s="5">
         <v>30</v>
@@ -1724,19 +1793,19 @@
         <v>3</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B36" s="5"/>
-      <c r="C36" s="5">
-        <v>30</v>
+      <c r="C36" s="5" t="s">
+        <v>157</v>
       </c>
       <c r="D36" s="5">
         <v>25</v>
@@ -1745,19 +1814,19 @@
         <v>2</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="63.75">
       <c r="A37" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B37" s="5"/>
-      <c r="C37" s="5">
-        <v>30</v>
+      <c r="C37" s="5" t="s">
+        <v>157</v>
       </c>
       <c r="D37" s="5">
         <v>10</v>
@@ -1766,19 +1835,19 @@
         <v>30</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B38" s="5"/>
-      <c r="C38" s="5">
-        <v>25</v>
+      <c r="C38" s="5" t="s">
+        <v>158</v>
       </c>
       <c r="D38" s="5">
         <v>10</v>
@@ -1787,19 +1856,19 @@
         <v>-5</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" s="5"/>
-      <c r="C39" s="5">
-        <v>20</v>
+      <c r="C39" s="5" t="s">
+        <v>159</v>
       </c>
       <c r="D39" s="5">
         <v>20</v>
@@ -1808,19 +1877,19 @@
         <v>20</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B40" s="5"/>
-      <c r="C40" s="5">
-        <v>15</v>
+      <c r="C40" s="5" t="s">
+        <v>160</v>
       </c>
       <c r="D40" s="5">
         <v>15</v>
@@ -1829,38 +1898,38 @@
         <v>5</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B41" s="5"/>
-      <c r="C41" s="5">
-        <v>15</v>
+      <c r="C41" s="5" t="s">
+        <v>160</v>
       </c>
       <c r="D41" s="5">
         <v>15</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B42" s="5"/>
-      <c r="C42" s="5">
-        <v>10</v>
+      <c r="C42" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="D42" s="5">
         <v>15</v>
@@ -1869,59 +1938,59 @@
         <v>45</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C43" s="5">
-        <v>10</v>
+        <v>28</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="D43" s="5">
         <v>10</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B44" s="5"/>
-      <c r="C44" s="5">
-        <v>10</v>
+      <c r="C44" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5">
         <v>30</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B45" s="5"/>
-      <c r="C45" s="5">
-        <v>10</v>
+      <c r="C45" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="D45" s="5">
         <v>15</v>
@@ -1930,19 +1999,19 @@
         <v>-10</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B46" s="5"/>
-      <c r="C46" s="5">
-        <v>9</v>
+      <c r="C46" s="5" t="s">
+        <v>162</v>
       </c>
       <c r="D46" s="5">
         <v>4</v>
@@ -1951,21 +2020,21 @@
         <v>2</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C47" s="5">
-        <v>9</v>
+      <c r="C47" s="5" t="s">
+        <v>162</v>
       </c>
       <c r="D47" s="5">
         <v>4</v>
@@ -1974,21 +2043,21 @@
         <v>2</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C48" s="5">
-        <v>9</v>
+      <c r="C48" s="5" t="s">
+        <v>162</v>
       </c>
       <c r="D48" s="5">
         <v>4</v>
@@ -1997,19 +2066,19 @@
         <v>2</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B49" s="5"/>
-      <c r="C49" s="5">
-        <v>7</v>
+      <c r="C49" s="5" t="s">
+        <v>163</v>
       </c>
       <c r="D49" s="5">
         <v>2</v>
@@ -2018,21 +2087,21 @@
         <v>3</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C50" s="5">
-        <v>7</v>
+        <v>28</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>163</v>
       </c>
       <c r="D50" s="5">
         <v>2</v>
@@ -2041,40 +2110,40 @@
         <v>3</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B51" s="5"/>
-      <c r="C51" s="5">
-        <v>5</v>
+      <c r="C51" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="D51" s="5">
         <v>7</v>
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C52" s="5">
-        <v>5</v>
+      <c r="C52" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="D52" s="5">
         <v>2</v>
@@ -2083,19 +2152,19 @@
         <v>3</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B53" s="5"/>
-      <c r="C53" s="5">
-        <v>5</v>
+      <c r="C53" s="5" t="s">
+        <v>164</v>
       </c>
       <c r="D53" s="5">
         <v>5</v>
@@ -2104,21 +2173,21 @@
         <v>3</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="28.15" customHeight="1">
       <c r="A54" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B54" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C54" s="5">
-        <v>4</v>
+      <c r="C54" s="5" t="s">
+        <v>165</v>
       </c>
       <c r="D54" s="5">
         <v>3</v>
@@ -2127,21 +2196,21 @@
         <v>3</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C55" s="5">
-        <v>1</v>
+        <v>52</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>166</v>
       </c>
       <c r="D55" s="5">
         <v>5</v>
@@ -2150,15 +2219,15 @@
         <v>-10</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -2167,214 +2236,214 @@
         <v>40</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B57" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>57</v>
       </c>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
       <c r="F57" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>59</v>
       </c>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
       <c r="F58" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="25.5">
       <c r="A59" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B59" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
       <c r="F59" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
       <c r="F60" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B61" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>65</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
       <c r="F61" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="38.25">
       <c r="A62" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B62" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>67</v>
       </c>
       <c r="C62" s="5"/>
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
       <c r="F62" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="25.5">
       <c r="A63" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B63" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
       <c r="F63" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>71</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5"/>
       <c r="E64" s="5"/>
       <c r="F64" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="25.5">
       <c r="A65" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="5" t="s">
         <v>72</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>73</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
       <c r="F65" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="25.5">
       <c r="A66" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>75</v>
       </c>
       <c r="C66" s="5"/>
       <c r="D66" s="5"/>
       <c r="E66" s="5"/>
       <c r="F66" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B67" s="5" t="s">
         <v>76</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>77</v>
       </c>
       <c r="C67" s="5"/>
       <c r="D67" s="5"/>
       <c r="E67" s="5"/>
       <c r="F67" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G67" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="G67" s="6" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="14.65" thickBot="1">
       <c r="A68" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B68" s="10" t="s">
         <v>78</v>
-      </c>
-      <c r="B68" s="10" t="s">
-        <v>79</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="10"/>
       <c r="E68" s="10"/>
       <c r="F68" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/食物_药数据.xlsx
+++ b/data-source/食物_药数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49B1EF74-5370-4BF0-8948-CA63A2FBC073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6116CF-B21F-438C-B411-28DF5FD1E4A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1611,7 +1611,7 @@
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="8" t="s">
         <v>29</v>
       </c>
       <c r="B27" s="5" t="s">

--- a/data-source/食物_药数据.xlsx
+++ b/data-source/食物_药数据.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6116CF-B21F-438C-B411-28DF5FD1E4A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E2917D-FA33-4870-A20D-5AF38048157F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="172">
   <si>
     <t>特殊效果</t>
   </si>
@@ -538,6 +538,23 @@
   </si>
   <si>
     <t>持续1</t>
+  </si>
+  <si>
+    <t>曼德拉草种：1</t>
+  </si>
+  <si>
+    <t>水井</t>
+  </si>
+  <si>
+    <t>空水瓶：1</t>
+  </si>
+  <si>
+    <t>烈酒</t>
+  </si>
+  <si>
+    <t xml:space="preserve">厨师营地配方：冬青果：10
+草药桌配方：山楂：5；小空瓶：1
+</t>
   </si>
 </sst>
 </file>
@@ -1090,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.265625" customWidth="1"/>
@@ -1667,10 +1684,10 @@
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5" t="s">
-        <v>102</v>
+        <v>167</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2236,35 +2253,33 @@
         <v>40</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="38.25">
       <c r="A57" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>56</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="B57" s="5"/>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
       <c r="F57" s="5" t="s">
-        <v>102</v>
+        <v>171</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
@@ -2276,12 +2291,12 @@
         <v>102</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="25.5">
-      <c r="A59" s="12" t="s">
-        <v>59</v>
+    <row r="59" spans="1:7">
+      <c r="A59" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
@@ -2293,12 +2308,12 @@
         <v>102</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
-      <c r="A60" s="8" t="s">
-        <v>61</v>
+    <row r="60" spans="1:7" ht="25.5">
+      <c r="A60" s="12" t="s">
+        <v>59</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
@@ -2311,11 +2326,11 @@
       </c>
     </row>
     <row r="61" spans="1:7">
-      <c r="A61" s="7" t="s">
-        <v>63</v>
+      <c r="A61" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
@@ -2327,12 +2342,12 @@
         <v>102</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="38.25">
-      <c r="A62" s="8" t="s">
-        <v>65</v>
+    <row r="62" spans="1:7">
+      <c r="A62" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C62" s="5"/>
       <c r="D62" s="5"/>
@@ -2344,12 +2359,12 @@
         <v>102</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="25.5">
-      <c r="A63" s="12" t="s">
-        <v>67</v>
+    <row r="63" spans="1:7" ht="38.25">
+      <c r="A63" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
@@ -2361,12 +2376,12 @@
         <v>102</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
-      <c r="A64" s="8" t="s">
-        <v>69</v>
+    <row r="64" spans="1:7" ht="25.5">
+      <c r="A64" s="12" t="s">
+        <v>67</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5"/>
@@ -2378,12 +2393,12 @@
         <v>102</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="25.5">
-      <c r="A65" s="12" t="s">
-        <v>71</v>
+    <row r="65" spans="1:7">
+      <c r="A65" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
@@ -2397,10 +2412,10 @@
     </row>
     <row r="66" spans="1:7" ht="25.5">
       <c r="A66" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C66" s="5"/>
       <c r="D66" s="5"/>
@@ -2412,37 +2427,54 @@
         <v>102</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
-      <c r="A67" s="8" t="s">
-        <v>75</v>
+    <row r="67" spans="1:7" ht="25.5">
+      <c r="A67" s="12" t="s">
+        <v>73</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C67" s="5"/>
       <c r="D67" s="5"/>
       <c r="E67" s="5"/>
       <c r="F67" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G67" s="6" t="s">
+      <c r="G68" s="6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="14.65" thickBot="1">
-      <c r="A68" s="9" t="s">
+    <row r="69" spans="1:7" ht="14.65" thickBot="1">
+      <c r="A69" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="B69" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="C68" s="10"/>
-      <c r="D68" s="10"/>
-      <c r="E68" s="10"/>
-      <c r="F68" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="G68" s="11" t="s">
+      <c r="C69" s="10"/>
+      <c r="D69" s="10"/>
+      <c r="E69" s="10"/>
+      <c r="F69" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="G69" s="11" t="s">
         <v>102</v>
       </c>
     </row>

--- a/data-source/食物_药数据.xlsx
+++ b/data-source/食物_药数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E2917D-FA33-4870-A20D-5AF38048157F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB08D44-8CD6-4231-AD33-B6F5CC109352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -123,9 +123,6 @@
     <t>苹果包夹心糖</t>
   </si>
   <si>
-    <t>攻击速度提高15%，持续15秒，20次中毒呕吐</t>
-  </si>
-  <si>
     <t>曼德拉草根</t>
   </si>
   <si>
@@ -555,6 +552,9 @@
     <t xml:space="preserve">厨师营地配方：冬青果：10
 草药桌配方：山楂：5；小空瓶：1
 </t>
+  </si>
+  <si>
+    <t>20次中毒呕吐</t>
   </si>
 </sst>
 </file>
@@ -1121,7 +1121,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="16.149999999999999" thickBot="1">
       <c r="A1" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
@@ -1132,25 +1132,25 @@
     </row>
     <row r="2" spans="1:7" ht="15" thickTop="1" thickBot="1">
       <c r="A2" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="F2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="25.9" thickTop="1">
@@ -1161,15 +1161,15 @@
         <v>2</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="38.25">
@@ -1183,10 +1183,10 @@
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1200,10 +1200,10 @@
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="51">
@@ -1214,15 +1214,15 @@
         <v>2</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1233,17 +1233,17 @@
         <v>9</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5">
         <v>40</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="25.5">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D8" s="5">
         <v>100</v>
@@ -1261,10 +1261,10 @@
         <v>10</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1273,34 +1273,34 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5">
         <v>40</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
       <c r="F10" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="25.5">
@@ -1309,17 +1309,17 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D11" s="5">
         <v>100</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" s="5">
         <v>80</v>
@@ -1337,10 +1337,10 @@
         <v>25</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D13" s="5">
         <v>75</v>
@@ -1358,10 +1358,10 @@
         <v>5</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="25.5">
@@ -1372,15 +1372,15 @@
         <v>9</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="25.5">
@@ -1391,17 +1391,17 @@
         <v>17</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5">
         <v>20</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D16" s="5">
         <v>70</v>
@@ -1419,10 +1419,10 @@
         <v>20</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D17" s="5">
         <v>40</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D18" s="5">
         <v>30</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D19" s="5">
         <v>10</v>
@@ -1478,10 +1478,10 @@
         <v>80</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="51">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D20" s="5">
         <v>30</v>
@@ -1499,10 +1499,10 @@
         <v>-3</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D21" s="5">
         <v>30</v>
@@ -1520,10 +1520,10 @@
         <v>-5</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1532,17 +1532,17 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D22" s="5">
         <v>30</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1551,17 +1551,17 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D23" s="5">
         <v>60</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="25.5">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D24" s="5">
         <v>45</v>
@@ -1579,10 +1579,10 @@
         <v>25</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D25" s="5">
         <v>45</v>
@@ -1600,31 +1600,31 @@
         <v>10</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5">
         <v>30</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1635,7 +1635,7 @@
         <v>30</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D27" s="5">
         <v>40</v>
@@ -1644,21 +1644,21 @@
         <v>-3</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="25.5">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" s="7" t="s">
         <v>31</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>32</v>
+        <v>171</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D28" s="5">
         <v>10</v>
@@ -1667,36 +1667,36 @@
         <v>-5</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D30" s="5">
         <v>37</v>
@@ -1705,21 +1705,21 @@
         <v>23</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="25.5">
       <c r="A31" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D31" s="5">
         <v>15</v>
@@ -1728,38 +1728,38 @@
         <v>10</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D32" s="5">
         <v>20</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D33" s="5">
         <v>40</v>
@@ -1768,19 +1768,19 @@
         <v>-3</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="25.5">
       <c r="A34" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D34" s="5">
         <v>40</v>
@@ -1789,19 +1789,19 @@
         <v>20</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D35" s="5">
         <v>30</v>
@@ -1810,19 +1810,19 @@
         <v>3</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D36" s="5">
         <v>25</v>
@@ -1831,19 +1831,19 @@
         <v>2</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="63.75">
       <c r="A37" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D37" s="5">
         <v>10</v>
@@ -1852,19 +1852,19 @@
         <v>30</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D38" s="5">
         <v>10</v>
@@ -1873,19 +1873,19 @@
         <v>-5</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D39" s="5">
         <v>20</v>
@@ -1894,19 +1894,19 @@
         <v>20</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D40" s="5">
         <v>15</v>
@@ -1915,38 +1915,38 @@
         <v>5</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D41" s="5">
         <v>15</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D42" s="5">
         <v>15</v>
@@ -1955,59 +1955,59 @@
         <v>45</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D43" s="5">
         <v>10</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5">
         <v>30</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D45" s="5">
         <v>15</v>
@@ -2016,19 +2016,19 @@
         <v>-10</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D46" s="5">
         <v>4</v>
@@ -2037,21 +2037,21 @@
         <v>2</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>47</v>
-      </c>
       <c r="C47" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D47" s="5">
         <v>4</v>
@@ -2060,21 +2060,21 @@
         <v>2</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="C48" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D48" s="5">
         <v>4</v>
@@ -2083,19 +2083,19 @@
         <v>2</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D49" s="5">
         <v>2</v>
@@ -2104,21 +2104,21 @@
         <v>3</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D50" s="5">
         <v>2</v>
@@ -2127,40 +2127,40 @@
         <v>3</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="12" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D51" s="5">
         <v>7</v>
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B52" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>52</v>
-      </c>
       <c r="C52" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D52" s="5">
         <v>2</v>
@@ -2169,19 +2169,19 @@
         <v>3</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D53" s="5">
         <v>5</v>
@@ -2190,21 +2190,21 @@
         <v>3</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="28.15" customHeight="1">
       <c r="A54" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B54" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="5" t="s">
-        <v>54</v>
-      </c>
       <c r="C54" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D54" s="5">
         <v>3</v>
@@ -2213,21 +2213,21 @@
         <v>3</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D55" s="5">
         <v>5</v>
@@ -2236,15 +2236,15 @@
         <v>-10</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -2253,229 +2253,229 @@
         <v>40</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="38.25">
       <c r="A57" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
       <c r="F57" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B58" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>56</v>
       </c>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
       <c r="F58" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B59" s="5" t="s">
         <v>57</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
       <c r="F59" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="25.5">
       <c r="A60" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>60</v>
       </c>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
       <c r="F60" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B61" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>62</v>
       </c>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
       <c r="F61" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B62" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="C62" s="5"/>
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
       <c r="F62" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="38.25">
       <c r="A63" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B63" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>66</v>
       </c>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
       <c r="F63" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="25.5">
       <c r="A64" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B64" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>68</v>
       </c>
       <c r="C64" s="5"/>
       <c r="D64" s="5"/>
       <c r="E64" s="5"/>
       <c r="F64" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B65" s="5" t="s">
         <v>69</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>70</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
       <c r="F65" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="25.5">
       <c r="A66" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B66" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>72</v>
       </c>
       <c r="C66" s="5"/>
       <c r="D66" s="5"/>
       <c r="E66" s="5"/>
       <c r="F66" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="25.5">
       <c r="A67" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B67" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>74</v>
       </c>
       <c r="C67" s="5"/>
       <c r="D67" s="5"/>
       <c r="E67" s="5"/>
       <c r="F67" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>76</v>
       </c>
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
       <c r="E68" s="5"/>
       <c r="F68" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G68" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="G68" s="6" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="14.65" thickBot="1">
       <c r="A69" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="B69" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="C69" s="10"/>
       <c r="D69" s="10"/>
       <c r="E69" s="10"/>
       <c r="F69" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
